--- a/artfynd/A 52979-2025 artfynd.xlsx
+++ b/artfynd/A 52979-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>129000500</v>
       </c>
       <c r="B4" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129000506</v>
+        <v>129000501</v>
       </c>
       <c r="B7" t="n">
         <v>79041</v>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>842150</v>
+        <v>842413</v>
       </c>
       <c r="R7" t="n">
-        <v>7467117</v>
+        <v>7466781</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129000501</v>
+        <v>129000506</v>
       </c>
       <c r="B8" t="n">
         <v>79041</v>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>842413</v>
+        <v>842150</v>
       </c>
       <c r="R8" t="n">
-        <v>7466781</v>
+        <v>7467117</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1420,7 +1420,7 @@
         <v>129000502</v>
       </c>
       <c r="B9" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>129000504</v>
       </c>
       <c r="B10" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129000507</v>
       </c>
       <c r="B13" t="n">
-        <v>91717</v>
+        <v>91726</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 52979-2025 artfynd.xlsx
+++ b/artfynd/A 52979-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129000505</v>
+        <v>129000498</v>
       </c>
       <c r="B2" t="n">
-        <v>82873</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>842145</v>
+        <v>842038</v>
       </c>
       <c r="R2" t="n">
-        <v>7467122</v>
+        <v>7466339</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129000498</v>
+        <v>129000500</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>97576</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>842038</v>
+        <v>842379</v>
       </c>
       <c r="R3" t="n">
-        <v>7466339</v>
+        <v>7466278</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000500</v>
+        <v>129000505</v>
       </c>
       <c r="B4" t="n">
-        <v>97575</v>
+        <v>82873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>842379</v>
+        <v>842145</v>
       </c>
       <c r="R4" t="n">
-        <v>7466278</v>
+        <v>7467122</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1420,7 +1420,7 @@
         <v>129000502</v>
       </c>
       <c r="B9" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>129000504</v>
       </c>
       <c r="B10" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129000507</v>
       </c>
       <c r="B13" t="n">
-        <v>91726</v>
+        <v>91727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 52979-2025 artfynd.xlsx
+++ b/artfynd/A 52979-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129000500</v>
       </c>
       <c r="B3" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>129000502</v>
       </c>
       <c r="B9" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>129000504</v>
       </c>
       <c r="B10" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 52979-2025 artfynd.xlsx
+++ b/artfynd/A 52979-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000498</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129000500</v>
+        <v>129000505</v>
       </c>
       <c r="B3" t="n">
-        <v>97577</v>
+        <v>82877</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>842379</v>
+        <v>842145</v>
       </c>
       <c r="R3" t="n">
-        <v>7466278</v>
+        <v>7467122</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000505</v>
+        <v>129000500</v>
       </c>
       <c r="B4" t="n">
-        <v>82873</v>
+        <v>97581</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>842145</v>
+        <v>842379</v>
       </c>
       <c r="R4" t="n">
-        <v>7467122</v>
+        <v>7466278</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -996,7 +996,7 @@
         <v>129000509</v>
       </c>
       <c r="B5" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>129000512</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129000501</v>
+        <v>129000502</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>97581</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>842413</v>
+        <v>842327</v>
       </c>
       <c r="R7" t="n">
-        <v>7466781</v>
+        <v>7466896</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129000506</v>
+        <v>129000501</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>842150</v>
+        <v>842413</v>
       </c>
       <c r="R8" t="n">
-        <v>7467117</v>
+        <v>7466781</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1417,37 +1417,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129000502</v>
+        <v>129000506</v>
       </c>
       <c r="B9" t="n">
-        <v>97577</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>842327</v>
+        <v>842150</v>
       </c>
       <c r="R9" t="n">
-        <v>7466896</v>
+        <v>7467117</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1526,7 +1526,7 @@
         <v>129000504</v>
       </c>
       <c r="B10" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>129000510</v>
       </c>
       <c r="B11" t="n">
-        <v>82873</v>
+        <v>82877</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>129000497</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129000507</v>
       </c>
       <c r="B13" t="n">
-        <v>91727</v>
+        <v>91730</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 52979-2025 artfynd.xlsx
+++ b/artfynd/A 52979-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000498</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129000505</v>
       </c>
       <c r="B3" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129000500</v>
       </c>
       <c r="B4" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129000509</v>
       </c>
       <c r="B5" t="n">
-        <v>83011</v>
+        <v>83012</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>129000512</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129000502</v>
+        <v>129000501</v>
       </c>
       <c r="B7" t="n">
-        <v>97581</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>842327</v>
+        <v>842413</v>
       </c>
       <c r="R7" t="n">
-        <v>7466896</v>
+        <v>7466781</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129000501</v>
+        <v>129000506</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>842413</v>
+        <v>842150</v>
       </c>
       <c r="R8" t="n">
-        <v>7466781</v>
+        <v>7467117</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1417,37 +1417,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129000506</v>
+        <v>129000502</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>97583</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>842150</v>
+        <v>842327</v>
       </c>
       <c r="R9" t="n">
-        <v>7467117</v>
+        <v>7466896</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1526,7 +1526,7 @@
         <v>129000504</v>
       </c>
       <c r="B10" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>129000510</v>
       </c>
       <c r="B11" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>129000497</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129000507</v>
       </c>
       <c r="B13" t="n">
-        <v>91730</v>
+        <v>91732</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 52979-2025 artfynd.xlsx
+++ b/artfynd/A 52979-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129000498</v>
+        <v>129000500</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>97587</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>842038</v>
+        <v>842379</v>
       </c>
       <c r="R2" t="n">
-        <v>7466339</v>
+        <v>7466278</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000500</v>
+        <v>129000498</v>
       </c>
       <c r="B4" t="n">
-        <v>97583</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>842379</v>
+        <v>842038</v>
       </c>
       <c r="R4" t="n">
-        <v>7466278</v>
+        <v>7466339</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1420,7 +1420,7 @@
         <v>129000502</v>
       </c>
       <c r="B9" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>129000504</v>
       </c>
       <c r="B10" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129000507</v>
       </c>
       <c r="B13" t="n">
-        <v>91732</v>
+        <v>91736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 52979-2025 artfynd.xlsx
+++ b/artfynd/A 52979-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129000500</v>
+        <v>129000498</v>
       </c>
       <c r="B2" t="n">
-        <v>97587</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>842379</v>
+        <v>842038</v>
       </c>
       <c r="R2" t="n">
-        <v>7466278</v>
+        <v>7466339</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129000505</v>
+        <v>129000500</v>
       </c>
       <c r="B3" t="n">
-        <v>82878</v>
+        <v>97595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>842145</v>
+        <v>842379</v>
       </c>
       <c r="R3" t="n">
-        <v>7467122</v>
+        <v>7466278</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000498</v>
+        <v>129000505</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>82878</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>842038</v>
+        <v>842145</v>
       </c>
       <c r="R4" t="n">
-        <v>7466339</v>
+        <v>7467122</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1420,7 +1420,7 @@
         <v>129000502</v>
       </c>
       <c r="B9" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>129000504</v>
       </c>
       <c r="B10" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129000507</v>
       </c>
       <c r="B13" t="n">
-        <v>91736</v>
+        <v>91737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 52979-2025 artfynd.xlsx
+++ b/artfynd/A 52979-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129000498</v>
+        <v>129000500</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>97595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>842038</v>
+        <v>842379</v>
       </c>
       <c r="R2" t="n">
-        <v>7466339</v>
+        <v>7466278</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129000500</v>
+        <v>129000498</v>
       </c>
       <c r="B3" t="n">
-        <v>97595</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>842379</v>
+        <v>842038</v>
       </c>
       <c r="R3" t="n">
-        <v>7466278</v>
+        <v>7466339</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129000501</v>
+        <v>129000506</v>
       </c>
       <c r="B7" t="n">
         <v>79044</v>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>842413</v>
+        <v>842150</v>
       </c>
       <c r="R7" t="n">
-        <v>7466781</v>
+        <v>7467117</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129000506</v>
+        <v>129000501</v>
       </c>
       <c r="B8" t="n">
         <v>79044</v>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>842150</v>
+        <v>842413</v>
       </c>
       <c r="R8" t="n">
-        <v>7467117</v>
+        <v>7466781</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>

--- a/artfynd/A 52979-2025 artfynd.xlsx
+++ b/artfynd/A 52979-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129000500</v>
+        <v>129000505</v>
       </c>
       <c r="B2" t="n">
-        <v>97595</v>
+        <v>82878</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>842379</v>
+        <v>842145</v>
       </c>
       <c r="R2" t="n">
-        <v>7466278</v>
+        <v>7467122</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000505</v>
+        <v>129000500</v>
       </c>
       <c r="B4" t="n">
-        <v>82878</v>
+        <v>97595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>842145</v>
+        <v>842379</v>
       </c>
       <c r="R4" t="n">
-        <v>7467122</v>
+        <v>7466278</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1205,37 +1205,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129000506</v>
+        <v>129000502</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>97595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>842150</v>
+        <v>842327</v>
       </c>
       <c r="R7" t="n">
-        <v>7467117</v>
+        <v>7466896</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129000501</v>
+        <v>129000506</v>
       </c>
       <c r="B8" t="n">
         <v>79044</v>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>842413</v>
+        <v>842150</v>
       </c>
       <c r="R8" t="n">
-        <v>7466781</v>
+        <v>7467117</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1417,32 +1417,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129000502</v>
+        <v>129000501</v>
       </c>
       <c r="B9" t="n">
-        <v>97595</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>842327</v>
+        <v>842413</v>
       </c>
       <c r="R9" t="n">
-        <v>7466896</v>
+        <v>7466781</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>

--- a/artfynd/A 52979-2025 artfynd.xlsx
+++ b/artfynd/A 52979-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129000505</v>
+        <v>129000500</v>
       </c>
       <c r="B2" t="n">
-        <v>82878</v>
+        <v>97598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>842145</v>
+        <v>842379</v>
       </c>
       <c r="R2" t="n">
-        <v>7467122</v>
+        <v>7466278</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129000498</v>
+        <v>129000505</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>82878</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>842038</v>
+        <v>842145</v>
       </c>
       <c r="R3" t="n">
-        <v>7466339</v>
+        <v>7467122</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000500</v>
+        <v>129000498</v>
       </c>
       <c r="B4" t="n">
-        <v>97595</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>842379</v>
+        <v>842038</v>
       </c>
       <c r="R4" t="n">
-        <v>7466278</v>
+        <v>7466339</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129000502</v>
+        <v>129000501</v>
       </c>
       <c r="B7" t="n">
-        <v>97595</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>842327</v>
+        <v>842413</v>
       </c>
       <c r="R7" t="n">
-        <v>7466896</v>
+        <v>7466781</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1417,32 +1417,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129000501</v>
+        <v>129000502</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>97598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>842413</v>
+        <v>842327</v>
       </c>
       <c r="R9" t="n">
-        <v>7466781</v>
+        <v>7466896</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1526,7 +1526,7 @@
         <v>129000504</v>
       </c>
       <c r="B10" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129000507</v>
       </c>
       <c r="B13" t="n">
-        <v>91737</v>
+        <v>91740</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 52979-2025 artfynd.xlsx
+++ b/artfynd/A 52979-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129000500</v>
+        <v>129000505</v>
       </c>
       <c r="B2" t="n">
-        <v>97598</v>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>842379</v>
+        <v>842145</v>
       </c>
       <c r="R2" t="n">
-        <v>7466278</v>
+        <v>7467122</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129000505</v>
+        <v>129000510</v>
       </c>
       <c r="B3" t="n">
-        <v>82878</v>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>842145</v>
+        <v>842147</v>
       </c>
       <c r="R3" t="n">
-        <v>7467122</v>
+        <v>7467294</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000498</v>
+        <v>129000503</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>92097</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1588</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,13 +926,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>842038</v>
+        <v>842187</v>
       </c>
       <c r="R4" t="n">
-        <v>7466339</v>
+        <v>7466946</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129000509</v>
+        <v>129000507</v>
       </c>
       <c r="B5" t="n">
-        <v>83012</v>
+        <v>92097</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>1588</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>842142</v>
+        <v>842144</v>
       </c>
       <c r="R5" t="n">
-        <v>7467295</v>
+        <v>7467291</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1099,14 +1099,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129000512</v>
+        <v>129000497</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>842144</v>
+        <v>841968</v>
       </c>
       <c r="R6" t="n">
-        <v>7467297</v>
+        <v>7466907</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1205,14 +1205,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129000501</v>
+        <v>129000498</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>842413</v>
+        <v>842038</v>
       </c>
       <c r="R7" t="n">
-        <v>7466781</v>
+        <v>7466339</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1314,11 +1314,11 @@
         <v>129000506</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1417,32 +1417,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129000502</v>
+        <v>129000512</v>
       </c>
       <c r="B9" t="n">
-        <v>97598</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>842327</v>
+        <v>842144</v>
       </c>
       <c r="R9" t="n">
-        <v>7466896</v>
+        <v>7467297</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1523,32 +1523,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129000504</v>
+        <v>129000509</v>
       </c>
       <c r="B10" t="n">
-        <v>97598</v>
+        <v>83307</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>842119</v>
+        <v>842142</v>
       </c>
       <c r="R10" t="n">
-        <v>7467097</v>
+        <v>7467295</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1629,37 +1629,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129000510</v>
+        <v>129000504</v>
       </c>
       <c r="B11" t="n">
-        <v>82878</v>
+        <v>97983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>842147</v>
+        <v>842119</v>
       </c>
       <c r="R11" t="n">
-        <v>7467294</v>
+        <v>7467097</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1735,14 +1735,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129000497</v>
+        <v>129000501</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1774,10 +1774,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>841968</v>
+        <v>842413</v>
       </c>
       <c r="R12" t="n">
-        <v>7466907</v>
+        <v>7466781</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1841,32 +1841,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129000507</v>
+        <v>129000500</v>
       </c>
       <c r="B13" t="n">
-        <v>91740</v>
+        <v>97983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1588</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>842144</v>
+        <v>842379</v>
       </c>
       <c r="R13" t="n">
-        <v>7467291</v>
+        <v>7466278</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1944,6 +1944,112 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129000502</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tärendö, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>842327</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7466896</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52979-2025 artfynd.xlsx
+++ b/artfynd/A 52979-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000505</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000510</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000503</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000507</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000497</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000498</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000501</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000506</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000512</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000509</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,6 +1893,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000500</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,6 +2004,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000502</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2050,8 +2115,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000504</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>